--- a/data/trans_orig/P20-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P20-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2007</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18441</t>
+          <t>17974</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19777</t>
+          <t>18758</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40955</t>
+          <t>40200</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27162</t>
+          <t>27129</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52775</t>
+          <t>51998</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>474679</t>
+          <t>475146</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>488276</t>
+          <t>488685</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>426534</t>
+          <t>427289</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>447712</t>
+          <t>448731</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>907834</t>
+          <t>908611</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>933447</t>
+          <t>933480</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14905</t>
+          <t>14913</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34366</t>
+          <t>34480</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59693</t>
+          <t>58818</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>92829</t>
+          <t>92415</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80176</t>
+          <t>79887</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>117679</t>
+          <t>118601</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>701123</t>
+          <t>701009</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>720584</t>
+          <t>720576</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>532665</t>
+          <t>533079</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>565801</t>
+          <t>566676</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1243303</t>
+          <t>1242381</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1280806</t>
+          <t>1281095</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,13%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11418</t>
+          <t>11259</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28970</t>
+          <t>27187</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24646</t>
+          <t>22876</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47896</t>
+          <t>46199</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39058</t>
+          <t>40186</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66399</t>
+          <t>67064</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>609698</t>
+          <t>611481</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>627250</t>
+          <t>627409</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>641848</t>
+          <t>643545</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>665098</t>
+          <t>666868</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1262013</t>
+          <t>1261348</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1289354</t>
+          <t>1288226</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14082</t>
+          <t>14333</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34446</t>
+          <t>34848</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17875</t>
+          <t>17412</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37392</t>
+          <t>37291</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35653</t>
+          <t>35285</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63311</t>
+          <t>64274</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>484701</t>
+          <t>484299</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>505065</t>
+          <t>504814</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>478250</t>
+          <t>478351</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>497767</t>
+          <t>498230</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>971478</t>
+          <t>970515</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>999136</t>
+          <t>999504</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12445</t>
+          <t>13225</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29029</t>
+          <t>28870</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16324</t>
+          <t>15390</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35975</t>
+          <t>35704</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32775</t>
+          <t>32421</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58309</t>
+          <t>57156</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>357681</t>
+          <t>357840</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>374265</t>
+          <t>373485</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>368011</t>
+          <t>368282</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>387662</t>
+          <t>388596</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>732387</t>
+          <t>733540</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>757921</t>
+          <t>758275</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,9%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14765</t>
+          <t>15714</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33112</t>
+          <t>33522</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21312</t>
+          <t>20252</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40455</t>
+          <t>39871</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40019</t>
+          <t>39558</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>68228</t>
+          <t>65549</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259471</t>
+          <t>259061</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>277818</t>
+          <t>276869</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>302479</t>
+          <t>303063</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>321622</t>
+          <t>322682</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>567289</t>
+          <t>569968</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>595498</t>
+          <t>595959</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,78%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12344</t>
+          <t>12310</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29016</t>
+          <t>29552</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23272</t>
+          <t>22673</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46579</t>
+          <t>46064</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39286</t>
+          <t>39215</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67313</t>
+          <t>67110</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>180867</t>
+          <t>180331</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>197539</t>
+          <t>197573</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>287329</t>
+          <t>287844</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>310636</t>
+          <t>311235</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>476478</t>
+          <t>476681</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>504505</t>
+          <t>504576</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,79%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>114463</t>
+          <t>114249</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>161027</t>
+          <t>160390</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>221883</t>
+          <t>221283</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>285315</t>
+          <t>281499</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>350217</t>
+          <t>347926</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>422044</t>
+          <t>424115</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3114572</t>
+          <t>3115209</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3161136</t>
+          <t>3161350</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3093882</t>
+          <t>3097698</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3157314</t>
+          <t>3157914</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6232752</t>
+          <t>6230681</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6304579</t>
+          <t>6306870</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2012</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2012 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24157</t>
+          <t>24848</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24499</t>
+          <t>24562</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48119</t>
+          <t>48205</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37355</t>
+          <t>37878</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66544</t>
+          <t>64751</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>427942</t>
+          <t>427251</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>443426</t>
+          <t>443283</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>382111</t>
+          <t>382025</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>405731</t>
+          <t>405668</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>815785</t>
+          <t>817578</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>844974</t>
+          <t>844451</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21557</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43762</t>
+          <t>44074</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71611</t>
+          <t>70021</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105450</t>
+          <t>105311</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97203</t>
+          <t>97311</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>141145</t>
+          <t>139380</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>643325</t>
+          <t>643013</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>665530</t>
+          <t>666217</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>504805</t>
+          <t>504944</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>538644</t>
+          <t>540234</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1156197</t>
+          <t>1157962</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1200139</t>
+          <t>1200031</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26148</t>
+          <t>26242</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53336</t>
+          <t>53627</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44150</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73778</t>
+          <t>73539</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75032</t>
+          <t>74411</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114278</t>
+          <t>114819</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>628527</t>
+          <t>628236</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>655715</t>
+          <t>655621</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>637072</t>
+          <t>637311</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>666700</t>
+          <t>667399</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1278434</t>
+          <t>1277893</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1317680</t>
+          <t>1318301</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23068</t>
+          <t>22506</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45920</t>
+          <t>45188</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36728</t>
+          <t>36922</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66995</t>
+          <t>67595</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66784</t>
+          <t>66686</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103617</t>
+          <t>102694</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>568697</t>
+          <t>569429</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>591549</t>
+          <t>592111</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>549204</t>
+          <t>548604</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>579471</t>
+          <t>579277</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1127199</t>
+          <t>1128122</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1164032</t>
+          <t>1164130</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,58%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18884</t>
+          <t>18750</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39624</t>
+          <t>38509</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20638</t>
+          <t>21475</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42407</t>
+          <t>42995</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44871</t>
+          <t>44885</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75494</t>
+          <t>74250</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>389805</t>
+          <t>390920</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>410545</t>
+          <t>410679</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>405393</t>
+          <t>404805</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>427162</t>
+          <t>426325</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>801735</t>
+          <t>802979</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>832358</t>
+          <t>832344</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20211</t>
+          <t>19637</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43372</t>
+          <t>40931</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23794</t>
+          <t>24402</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45078</t>
+          <t>46060</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48366</t>
+          <t>48988</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79604</t>
+          <t>80141</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>266414</t>
+          <t>268855</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>289575</t>
+          <t>290149</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>308918</t>
+          <t>307936</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>330202</t>
+          <t>329594</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>584178</t>
+          <t>583641</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>615416</t>
+          <t>614794</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,62%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25526</t>
+          <t>25416</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50605</t>
+          <t>49815</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33319</t>
+          <t>31992</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>59490</t>
+          <t>57681</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65286</t>
+          <t>64873</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>99604</t>
+          <t>100318</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>199246</t>
+          <t>200036</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>224325</t>
+          <t>224435</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>329489</t>
+          <t>331298</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>355660</t>
+          <t>356987</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>539226</t>
+          <t>538512</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>573544</t>
+          <t>573957</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,85%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>181142</t>
+          <t>179576</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>240563</t>
+          <t>238955</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>304031</t>
+          <t>305250</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>374818</t>
+          <t>377915</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>501689</t>
+          <t>498597</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>591963</t>
+          <t>594004</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3184168</t>
+          <t>3185776</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3243589</t>
+          <t>3245155</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3183491</t>
+          <t>3180394</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3254278</t>
+          <t>3253059</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6391077</t>
+          <t>6389036</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6481351</t>
+          <t>6484443</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2016</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>6779</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21254</t>
+          <t>20676</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23915</t>
+          <t>24218</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46404</t>
+          <t>47128</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35091</t>
+          <t>34471</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62899</t>
+          <t>61877</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>398209</t>
+          <t>398787</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>413032</t>
+          <t>412684</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>349351</t>
+          <t>348627</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>371840</t>
+          <t>371537</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>752319</t>
+          <t>753341</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>780127</t>
+          <t>780747</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6969</t>
+          <t>7085</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22895</t>
+          <t>23787</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48044</t>
+          <t>47266</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78544</t>
+          <t>76949</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60111</t>
+          <t>58331</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93595</t>
+          <t>91569</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>567601</t>
+          <t>566709</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>583527</t>
+          <t>583411</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>485000</t>
+          <t>486595</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>515500</t>
+          <t>516278</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1060445</t>
+          <t>1062471</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1093929</t>
+          <t>1095709</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,95%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>14684</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35045</t>
+          <t>35360</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38099</t>
+          <t>39337</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66855</t>
+          <t>66768</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59280</t>
+          <t>57794</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93631</t>
+          <t>94406</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>634052</t>
+          <t>633737</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>654973</t>
+          <t>654413</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>594531</t>
+          <t>594618</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>623287</t>
+          <t>622049</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1236852</t>
+          <t>1236077</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1271203</t>
+          <t>1272689</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14079</t>
+          <t>14668</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33442</t>
+          <t>33603</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22097</t>
+          <t>21607</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44542</t>
+          <t>46521</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40829</t>
+          <t>40064</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70670</t>
+          <t>69613</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>612606</t>
+          <t>612445</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>631969</t>
+          <t>631380</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>604535</t>
+          <t>602556</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>626980</t>
+          <t>627470</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1224455</t>
+          <t>1225512</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1254296</t>
+          <t>1255061</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23482</t>
+          <t>23891</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47748</t>
+          <t>47616</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>16487</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36693</t>
+          <t>37151</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46188</t>
+          <t>43298</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75710</t>
+          <t>76634</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>430170</t>
+          <t>430302</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>454436</t>
+          <t>454027</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>460156</t>
+          <t>459698</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>479606</t>
+          <t>480362</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>899057</t>
+          <t>898133</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>928579</t>
+          <t>931469</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25887</t>
+          <t>25930</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49759</t>
+          <t>50233</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,47 +8421,47 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>15,02%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>29229</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>19753</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>41027</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
           <t>7,74%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>14,88%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>29229</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>19955</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>43399</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>7,74%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50756</t>
+          <t>51011</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81732</t>
+          <t>83281</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>284571</t>
+          <t>284097</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>308443</t>
+          <t>308400</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,47 +8534,47 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>92,24%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>348533</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>336735</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>358009</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
           <t>92,26%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>348533</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>334363</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>357807</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>92,26%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>630360</t>
+          <t>628811</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>661336</t>
+          <t>661081</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,84%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14251</t>
+          <t>14775</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30976</t>
+          <t>31512</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28402</t>
+          <t>27725</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57416</t>
+          <t>54933</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46416</t>
+          <t>47631</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79963</t>
+          <t>78647</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>226022</t>
+          <t>225486</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>242747</t>
+          <t>242223</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>342753</t>
+          <t>345236</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>371767</t>
+          <t>372444</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>577204</t>
+          <t>578520</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>610751</t>
+          <t>609536</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,75%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>138465</t>
+          <t>138742</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>190218</t>
+          <t>189650</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>241903</t>
+          <t>242355</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>306475</t>
+          <t>309016</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>396890</t>
+          <t>396945</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>477952</t>
+          <t>480834</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3204132</t>
+          <t>3204700</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3255885</t>
+          <t>3255608</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3238067</t>
+          <t>3235526</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3302639</t>
+          <t>3302187</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6460940</t>
+          <t>6458058</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6542002</t>
+          <t>6541947</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2023</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2023 (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7592</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12301</t>
+          <t>12390</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39813</t>
+          <t>38631</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12336</t>
+          <t>12367</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40842</t>
+          <t>41404</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>392395</t>
+          <t>392440</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273387</t>
+          <t>274569</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>300899</t>
+          <t>300810</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>672345</t>
+          <t>671783</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>700851</t>
+          <t>700820</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6494</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28983</t>
+          <t>29853</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22429</t>
+          <t>22627</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52650</t>
+          <t>52564</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37368</t>
+          <t>36719</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72625</t>
+          <t>71683</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>394564</t>
+          <t>393694</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417053</t>
+          <t>416489</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>458854</t>
+          <t>458940</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>489075</t>
+          <t>488877</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>862426</t>
+          <t>863368</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>897683</t>
+          <t>898332</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12281</t>
+          <t>12843</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32579</t>
+          <t>32357</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27170</t>
+          <t>27106</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47380</t>
+          <t>46114</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44187</t>
+          <t>44689</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70345</t>
+          <t>72215</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>503759</t>
+          <t>503981</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>524057</t>
+          <t>523495</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>495088</t>
+          <t>496354</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>515298</t>
+          <t>515362</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1008461</t>
+          <t>1006591</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1034619</t>
+          <t>1034117</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15421</t>
+          <t>14146</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58344</t>
+          <t>58009</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21285</t>
+          <t>21742</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38833</t>
+          <t>38025</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40854</t>
+          <t>39680</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86203</t>
+          <t>87761</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>829442</t>
+          <t>829777</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>872365</t>
+          <t>873640</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>674048</t>
+          <t>674856</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>691596</t>
+          <t>691139</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1514464</t>
+          <t>1512906</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1559813</t>
+          <t>1560987</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34340</t>
+          <t>35028</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59368</t>
+          <t>58971</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21978</t>
+          <t>22020</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37255</t>
+          <t>38260</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62404</t>
+          <t>61900</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>91683</t>
+          <t>92105</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>501866</t>
+          <t>502263</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>526894</t>
+          <t>526206</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>508311</t>
+          <t>507306</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>523588</t>
+          <t>523546</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1015116</t>
+          <t>1014694</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1044395</t>
+          <t>1044899</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26461</t>
+          <t>27476</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44188</t>
+          <t>46076</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7741</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36991</t>
+          <t>37569</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28889</t>
+          <t>28518</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77774</t>
+          <t>77922</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>323977</t>
+          <t>322089</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>341704</t>
+          <t>340689</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>571377</t>
+          <t>570799</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>600627</t>
+          <t>599159</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>898759</t>
+          <t>898611</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>947644</t>
+          <t>948015</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23238</t>
+          <t>23611</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39596</t>
+          <t>39806</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32776</t>
+          <t>32440</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50861</t>
+          <t>49797</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59515</t>
+          <t>60563</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84479</t>
+          <t>85840</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,11%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>243163</t>
+          <t>242953</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>259521</t>
+          <t>259148</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>374970</t>
+          <t>376034</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>393055</t>
+          <t>393391</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>624111</t>
+          <t>622750</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>649075</t>
+          <t>648027</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,45%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>148604</t>
+          <t>147065</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>219461</t>
+          <t>219115</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>177874</t>
+          <t>175872</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>249496</t>
+          <t>249986</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,47 +12121,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>6,83%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>404902</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>346082</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>448675</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>5,69%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>4,86%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>6,82%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>572</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>404902</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>348675</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>450091</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>5,69%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3240356</t>
+          <t>3240702</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3311213</t>
+          <t>3312752</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3410321</t>
+          <t>3409831</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3481943</t>
+          <t>3483945</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,47 +12234,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
+          <t>95,19%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>8167</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>6714732</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>6670959</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>6773552</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>94,31%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>93,7%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>95,14%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>8167</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>6714732</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>6669543</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>6770959</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>94,31%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>93,68%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>95,1%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P20-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P20-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17974</t>
+          <t>19958</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18758</t>
+          <t>19677</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40200</t>
+          <t>41718</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27129</t>
+          <t>26695</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51998</t>
+          <t>52882</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>475146</t>
+          <t>473162</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>488685</t>
+          <t>488240</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>427289</t>
+          <t>425771</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>448731</t>
+          <t>447812</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>908611</t>
+          <t>907727</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>933480</t>
+          <t>933914</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14913</t>
+          <t>15327</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34480</t>
+          <t>34732</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58818</t>
+          <t>59818</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>92415</t>
+          <t>92782</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79887</t>
+          <t>79041</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>118601</t>
+          <t>117438</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>701009</t>
+          <t>700757</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>720576</t>
+          <t>720162</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>533079</t>
+          <t>532712</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>566676</t>
+          <t>565676</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1242381</t>
+          <t>1243544</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1281095</t>
+          <t>1281941</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,19%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11259</t>
+          <t>11031</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27187</t>
+          <t>27373</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22876</t>
+          <t>24330</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46199</t>
+          <t>47384</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40186</t>
+          <t>40082</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67064</t>
+          <t>68046</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>611481</t>
+          <t>611295</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>627409</t>
+          <t>627637</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>643545</t>
+          <t>642360</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>666868</t>
+          <t>665414</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1261348</t>
+          <t>1260366</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1288226</t>
+          <t>1288330</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14333</t>
+          <t>14343</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34848</t>
+          <t>34311</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17412</t>
+          <t>17281</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37291</t>
+          <t>37258</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35285</t>
+          <t>36826</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64274</t>
+          <t>64793</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>484299</t>
+          <t>484836</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>504814</t>
+          <t>504804</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>478351</t>
+          <t>478384</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>498230</t>
+          <t>498361</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>970515</t>
+          <t>969996</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>999504</t>
+          <t>997963</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13225</t>
+          <t>12069</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28870</t>
+          <t>28408</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15390</t>
+          <t>16692</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35704</t>
+          <t>37297</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32421</t>
+          <t>33102</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57156</t>
+          <t>57675</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>357840</t>
+          <t>358302</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>373485</t>
+          <t>374641</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>368282</t>
+          <t>366689</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>388596</t>
+          <t>387294</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>733540</t>
+          <t>733021</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>758275</t>
+          <t>757594</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15714</t>
+          <t>14898</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33522</t>
+          <t>33543</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20252</t>
+          <t>20330</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39871</t>
+          <t>40919</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39558</t>
+          <t>40907</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>65549</t>
+          <t>66233</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259061</t>
+          <t>259040</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>276869</t>
+          <t>277685</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>303063</t>
+          <t>302015</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>322682</t>
+          <t>322604</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>569968</t>
+          <t>569284</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>595959</t>
+          <t>594610</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,56%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12310</t>
+          <t>12019</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29552</t>
+          <t>29321</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22673</t>
+          <t>22839</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46064</t>
+          <t>46490</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39215</t>
+          <t>39586</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67110</t>
+          <t>68360</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,57%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>180331</t>
+          <t>180562</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>197573</t>
+          <t>197864</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>287844</t>
+          <t>287418</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>311235</t>
+          <t>311069</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>476681</t>
+          <t>475431</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>504576</t>
+          <t>504205</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>114249</t>
+          <t>113852</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>160390</t>
+          <t>161439</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>221283</t>
+          <t>217521</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>281499</t>
+          <t>281291</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>347926</t>
+          <t>345434</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>424115</t>
+          <t>423699</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3115209</t>
+          <t>3114160</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3161350</t>
+          <t>3161747</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3097698</t>
+          <t>3097906</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3157914</t>
+          <t>3161676</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6230681</t>
+          <t>6231097</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6306870</t>
+          <t>6309362</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24848</t>
+          <t>23616</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24562</t>
+          <t>25400</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48205</t>
+          <t>48380</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37878</t>
+          <t>37705</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64751</t>
+          <t>64764</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>427251</t>
+          <t>428483</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>443283</t>
+          <t>443215</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>382025</t>
+          <t>381850</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>405668</t>
+          <t>404830</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>817578</t>
+          <t>817565</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>844451</t>
+          <t>844624</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20870</t>
+          <t>20811</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44074</t>
+          <t>43593</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70021</t>
+          <t>69051</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105311</t>
+          <t>105793</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97311</t>
+          <t>98565</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>139380</t>
+          <t>140716</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>643013</t>
+          <t>643494</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>666217</t>
+          <t>666276</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>504944</t>
+          <t>504462</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>540234</t>
+          <t>541204</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1157962</t>
+          <t>1156626</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1200031</t>
+          <t>1198777</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26242</t>
+          <t>25720</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53627</t>
+          <t>53324</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43134</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73539</t>
+          <t>72860</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74411</t>
+          <t>74824</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114819</t>
+          <t>113855</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>628236</t>
+          <t>628539</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>655621</t>
+          <t>656143</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>637311</t>
+          <t>637990</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>667399</t>
+          <t>667716</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1277893</t>
+          <t>1278857</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1318301</t>
+          <t>1317888</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,63%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22506</t>
+          <t>22500</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45188</t>
+          <t>45679</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36922</t>
+          <t>38502</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67595</t>
+          <t>68672</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66686</t>
+          <t>67263</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102694</t>
+          <t>104967</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>569429</t>
+          <t>568938</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>592111</t>
+          <t>592117</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>548604</t>
+          <t>547527</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>579277</t>
+          <t>577697</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1128122</t>
+          <t>1125849</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1164130</t>
+          <t>1163553</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18750</t>
+          <t>17920</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38509</t>
+          <t>39365</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21475</t>
+          <t>20505</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42995</t>
+          <t>41561</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44885</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74250</t>
+          <t>72683</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>390920</t>
+          <t>390064</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>410679</t>
+          <t>411509</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>404805</t>
+          <t>406239</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>426325</t>
+          <t>427295</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>802979</t>
+          <t>804546</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>832344</t>
+          <t>831567</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19637</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40931</t>
+          <t>41551</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24402</t>
+          <t>24253</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46060</t>
+          <t>45507</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48988</t>
+          <t>49656</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80141</t>
+          <t>80227</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>268855</t>
+          <t>268235</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>290149</t>
+          <t>289857</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>307936</t>
+          <t>308489</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>329594</t>
+          <t>329743</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>583641</t>
+          <t>583555</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>614794</t>
+          <t>614126</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25416</t>
+          <t>25463</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49815</t>
+          <t>50805</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31992</t>
+          <t>33221</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57681</t>
+          <t>60241</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64873</t>
+          <t>62251</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>100318</t>
+          <t>100315</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>200036</t>
+          <t>199046</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>224435</t>
+          <t>224388</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>331298</t>
+          <t>328738</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>356987</t>
+          <t>355758</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>538512</t>
+          <t>538515</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>573957</t>
+          <t>576579</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,26%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>179576</t>
+          <t>182917</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>238955</t>
+          <t>241405</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>305250</t>
+          <t>304653</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>377915</t>
+          <t>372775</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>498597</t>
+          <t>501056</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>594004</t>
+          <t>597539</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3185776</t>
+          <t>3183326</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3245155</t>
+          <t>3241814</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3180394</t>
+          <t>3185534</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3253059</t>
+          <t>3253656</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6389036</t>
+          <t>6385501</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6484443</t>
+          <t>6481984</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,82%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6779</t>
+          <t>6643</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20676</t>
+          <t>20414</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24218</t>
+          <t>23597</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47128</t>
+          <t>46335</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34471</t>
+          <t>33794</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61877</t>
+          <t>59515</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>398787</t>
+          <t>399049</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>412684</t>
+          <t>412820</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>348627</t>
+          <t>349420</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>371537</t>
+          <t>372158</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>753341</t>
+          <t>755703</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>780747</t>
+          <t>781424</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7085</t>
+          <t>6893</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23787</t>
+          <t>23360</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47266</t>
+          <t>46922</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76949</t>
+          <t>76267</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58331</t>
+          <t>59830</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91569</t>
+          <t>92815</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>566709</t>
+          <t>567136</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>583411</t>
+          <t>583603</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>486595</t>
+          <t>487277</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>516278</t>
+          <t>516622</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1062471</t>
+          <t>1061225</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1095709</t>
+          <t>1094210</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14684</t>
+          <t>14430</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35360</t>
+          <t>34340</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39337</t>
+          <t>37991</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66768</t>
+          <t>66705</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57794</t>
+          <t>60435</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94406</t>
+          <t>95280</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>633737</t>
+          <t>634757</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>654413</t>
+          <t>654667</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>594618</t>
+          <t>594681</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>622049</t>
+          <t>623395</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1236077</t>
+          <t>1235203</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1272689</t>
+          <t>1270048</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14668</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33603</t>
+          <t>31945</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21607</t>
+          <t>21370</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46521</t>
+          <t>44311</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40064</t>
+          <t>41110</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69613</t>
+          <t>72448</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>612445</t>
+          <t>614103</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>631380</t>
+          <t>631616</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>602556</t>
+          <t>604766</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>627470</t>
+          <t>627707</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1225512</t>
+          <t>1222677</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1255061</t>
+          <t>1254015</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23891</t>
+          <t>23992</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47616</t>
+          <t>47408</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16487</t>
+          <t>16432</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37151</t>
+          <t>36833</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43298</t>
+          <t>42599</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76634</t>
+          <t>74283</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>430302</t>
+          <t>430510</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>454027</t>
+          <t>453926</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>459698</t>
+          <t>460016</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>480362</t>
+          <t>480417</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>898133</t>
+          <t>900484</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>931469</t>
+          <t>932168</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25930</t>
+          <t>25918</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50233</t>
+          <t>50715</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19753</t>
+          <t>19766</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41027</t>
+          <t>41863</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51011</t>
+          <t>50779</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>83281</t>
+          <t>84118</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>284097</t>
+          <t>283615</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>308400</t>
+          <t>308412</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>336735</t>
+          <t>335899</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>358009</t>
+          <t>357996</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>628811</t>
+          <t>627974</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>661081</t>
+          <t>661313</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,87%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14775</t>
+          <t>14312</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31512</t>
+          <t>30938</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27725</t>
+          <t>27086</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54933</t>
+          <t>55529</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47631</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78647</t>
+          <t>78586</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>225486</t>
+          <t>226060</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>242223</t>
+          <t>242686</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>345236</t>
+          <t>344640</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>372444</t>
+          <t>373083</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>578520</t>
+          <t>578581</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>609536</t>
+          <t>609797</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,79%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>138742</t>
+          <t>140882</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>189650</t>
+          <t>189532</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>242355</t>
+          <t>243318</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>309016</t>
+          <t>308758</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>396945</t>
+          <t>395829</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>480834</t>
+          <t>484261</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3204700</t>
+          <t>3204818</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3255608</t>
+          <t>3253468</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3235526</t>
+          <t>3235784</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3302187</t>
+          <t>3301224</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6458058</t>
+          <t>6454631</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6541947</t>
+          <t>6543063</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>6671</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22114</t>
+          <t>26129</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12390</t>
+          <t>13619</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38631</t>
+          <t>44963</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>23568</t>
+          <t>27429</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12367</t>
+          <t>14791</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41404</t>
+          <t>47219</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>398533</t>
+          <t>406492</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>392440</t>
+          <t>401122</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>291086</t>
+          <t>336383</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274569</t>
+          <t>317549</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>300810</t>
+          <t>348893</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>689619</t>
+          <t>742876</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>671783</t>
+          <t>723086</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>700820</t>
+          <t>755514</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15123</t>
+          <t>16973</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7058</t>
+          <t>7654</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29853</t>
+          <t>32013</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>42961</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22627</t>
+          <t>30996</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52564</t>
+          <t>58980</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>52515</t>
+          <t>59934</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36719</t>
+          <t>45628</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71683</t>
+          <t>80203</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>408424</t>
+          <t>459917</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>393694</t>
+          <t>444877</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>416489</t>
+          <t>469236</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>474111</t>
+          <t>458122</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>458940</t>
+          <t>442103</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>488877</t>
+          <t>470087</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>882536</t>
+          <t>918039</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>863368</t>
+          <t>897770</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>898332</t>
+          <t>932345</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,22 +10351,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>23900</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12843</t>
+          <t>14866</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32357</t>
+          <t>36322</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>35763</t>
+          <t>40938</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27106</t>
+          <t>31300</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46114</t>
+          <t>52397</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>57110</t>
+          <t>64838</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44689</t>
+          <t>51630</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72215</t>
+          <t>82508</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -10464,27 +10464,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>514991</t>
+          <t>596937</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>503981</t>
+          <t>584515</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>523495</t>
+          <t>605971</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>506705</t>
+          <t>581201</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>496354</t>
+          <t>569742</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>515362</t>
+          <t>590839</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1021696</t>
+          <t>1178138</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1006591</t>
+          <t>1160468</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1034117</t>
+          <t>1191346</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37480</t>
+          <t>42508</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14146</t>
+          <t>30770</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58009</t>
+          <t>58930</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>32515</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21742</t>
+          <t>24530</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38025</t>
+          <t>41986</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>66648</t>
+          <t>75023</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39680</t>
+          <t>60284</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>87761</t>
+          <t>92868</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>850306</t>
+          <t>658109</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>829777</t>
+          <t>641687</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>873640</t>
+          <t>669847</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>683713</t>
+          <t>704371</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>674856</t>
+          <t>694900</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>691139</t>
+          <t>712356</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1534019</t>
+          <t>1362481</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1512906</t>
+          <t>1344636</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1560987</t>
+          <t>1377220</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>46592</t>
+          <t>49964</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35028</t>
+          <t>38348</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58971</t>
+          <t>66180</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>29085</t>
+          <t>33216</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22020</t>
+          <t>25331</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38260</t>
+          <t>43268</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>75677</t>
+          <t>83180</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61900</t>
+          <t>69252</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>92105</t>
+          <t>100073</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>514642</t>
+          <t>559382</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>502263</t>
+          <t>543166</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>526206</t>
+          <t>570998</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>516481</t>
+          <t>574917</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>507306</t>
+          <t>564865</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>523546</t>
+          <t>582802</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1031122</t>
+          <t>1134299</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1014694</t>
+          <t>1117406</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1044899</t>
+          <t>1148227</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1106799</t>
+          <t>1217479</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1106799</t>
+          <t>1217479</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1106799</t>
+          <t>1217479</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>35239</t>
+          <t>37849</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27476</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46076</t>
+          <t>49107</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>22335</t>
+          <t>25630</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>19225</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37569</t>
+          <t>33779</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>57575</t>
+          <t>63479</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28518</t>
+          <t>51959</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77922</t>
+          <t>76102</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>332926</t>
+          <t>369231</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>322089</t>
+          <t>357973</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>340689</t>
+          <t>378152</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>586033</t>
+          <t>413536</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>570799</t>
+          <t>405387</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>599159</t>
+          <t>419941</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>918958</t>
+          <t>782767</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>898611</t>
+          <t>770144</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>948015</t>
+          <t>794287</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>93,86%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>30823</t>
+          <t>32683</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23611</t>
+          <t>24791</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39806</t>
+          <t>43236</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>40984</t>
+          <t>44078</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32440</t>
+          <t>35131</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49797</t>
+          <t>53542</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>71808</t>
+          <t>76762</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60563</t>
+          <t>65159</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85840</t>
+          <t>90385</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>251936</t>
+          <t>277515</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>242953</t>
+          <t>266962</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>259148</t>
+          <t>285407</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>384847</t>
+          <t>420531</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>376034</t>
+          <t>411067</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>393391</t>
+          <t>429478</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>636782</t>
+          <t>698045</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>622750</t>
+          <t>684422</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>648027</t>
+          <t>709648</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,59%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>188058</t>
+          <t>205178</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>147065</t>
+          <t>179132</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>219115</t>
+          <t>233033</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>216843</t>
+          <t>245467</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>175872</t>
+          <t>218887</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>249986</t>
+          <t>275599</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>404902</t>
+          <t>450645</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>346082</t>
+          <t>411442</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>448675</t>
+          <t>487883</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3271759</t>
+          <t>3327584</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3240702</t>
+          <t>3299729</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3312752</t>
+          <t>3353630</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3442974</t>
+          <t>3489062</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3409831</t>
+          <t>3458930</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3483945</t>
+          <t>3515642</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6714732</t>
+          <t>6816646</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6670959</t>
+          <t>6779408</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6773552</t>
+          <t>6855849</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3659817</t>
+          <t>3734529</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3659817</t>
+          <t>3734529</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3659817</t>
+          <t>3734529</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7119634</t>
+          <t>7267291</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7119634</t>
+          <t>7267291</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7119634</t>
+          <t>7267291</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
